--- a/OutputFile/LetFunction.xlsx
+++ b/OutputFile/LetFunction.xlsx
@@ -15,6 +15,7 @@
   <x:sheets>
     <x:sheet name="LetFunction" sheetId="2" r:id="rId1"/>
     <x:sheet name="SumOfSpecificCloumnValue" sheetId="5" r:id="rId5"/>
+    <x:sheet name="DuplicateRowRemoved" sheetId="6" r:id="rId6"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="0"/>
@@ -154,6 +155,9 @@
   </x:si>
   <x:si>
     <x:t>95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -705,4 +709,119 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D7"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0">
+        <x:v>1452</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="0">
+        <x:v>2541</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="0">
+        <x:v>7412</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0">
+        <x:v>8521</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0">
+        <x:v>1235</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0">
+        <x:v>1596</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>